--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484301_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484301_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3966</v>
+        <v>0.4292</v>
       </c>
       <c r="E2" t="n">
-        <v>1.234</v>
+        <v>-0.4343</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8373</v>
+        <v>0.8635</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4517</v>
+        <v>0.8105</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6907</v>
+        <v>0.0276</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.239</v>
+        <v>0.7829</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1088</v>
+        <v>1.7139</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7286</v>
+        <v>1.0655</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6198</v>
+        <v>0.6484</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.6571</v>
+        <v>-0.9034</v>
       </c>
       <c r="N2" t="n">
         <v>-1.0379</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.6192</v>
+        <v>0.1344</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3907</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.1488</v>
+        <v>-3.3208</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5395</v>
+        <v>2.1488</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.701</v>
+        <v>-0.1287</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2805</v>
+        <v>-0.046</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4205</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2553</v>
+        <v>0.9195</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5545</v>
+        <v>1.2186</v>
       </c>
       <c r="X2" t="n">
         <v>-0.2992</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. POCULL DURAN</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1512</v>
+        <v>0.2943</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0004</v>
+        <v>1.2133</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1508</v>
+        <v>-0.919</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.07870000000000001</v>
+        <v>0.4517</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.254</v>
+        <v>2.6907</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1753</v>
+        <v>-2.239</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0609</v>
+        <v>3.1088</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0205</v>
+        <v>3.7286</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0405</v>
+        <v>-0.6198</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1397</v>
+        <v>-2.6571</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2745</v>
+        <v>-1.0379</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1348</v>
+        <v>-1.6192</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.1488</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1953</v>
+        <v>2.5395</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0346</v>
+        <v>-0.8034</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0605</v>
+        <v>-0.3012</v>
       </c>
       <c r="U3" t="n">
-        <v>0.09520000000000001</v>
+        <v>-0.5022</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.2553</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.2992</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>L. POCULL DURAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1041</v>
+        <v>0.1028</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8587</v>
+        <v>0.0609</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7546</v>
+        <v>0.0419</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8105</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0276</v>
+        <v>-0.254</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7829</v>
+        <v>0.1753</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7139</v>
+        <v>0.0609</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0655</v>
+        <v>0.0205</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6484</v>
+        <v>0.0405</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9034</v>
+        <v>-0.1397</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0379</v>
+        <v>-0.2745</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1344</v>
+        <v>0.1348</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.3208</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1488</v>
+        <v>0.1953</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.662</v>
+        <v>-0.0138</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4704</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1916</v>
+        <v>-0.0138</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9195</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ QUILEZ</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.5742</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9968</v>
+        <v>0.4847</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3148</v>
+        <v>-1.0588</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1054</v>
+        <v>-2.0766</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0698</v>
+        <v>0.23</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1753</v>
+        <v>-2.3065</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0405</v>
+        <v>1.3801</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.7188</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0405</v>
+        <v>0.6613</v>
       </c>
       <c r="M5" t="n">
-        <v>0.065</v>
+        <v>-3.4567</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0698</v>
+        <v>-0.4889</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1348</v>
+        <v>-2.9678</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1953</v>
+        <v>2.5395</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0701</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0605</v>
+        <v>-0.1058</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0545</v>
+        <v>0.0357</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.9865</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.1638</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.1773</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>A. FERNANDEZ QUILEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0904</v>
+        <v>-0.6002999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4582</v>
+        <v>-0.9968</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5485</v>
+        <v>0.3965</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.1792</v>
+        <v>0.1054</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8416</v>
+        <v>-0.0698</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3375</v>
+        <v>0.1753</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6222</v>
+        <v>0.0405</v>
       </c>
       <c r="K6" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7422</v>
+        <v>0.0405</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.8014</v>
+        <v>0.065</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.7217</v>
+        <v>-0.0698</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0797</v>
+        <v>0.1348</v>
       </c>
       <c r="P6" t="n">
         <v>-0.7814</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.3208</v>
+        <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5395</v>
+        <v>0.1953</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1711</v>
+        <v>0.0757</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2805</v>
+        <v>-0.0605</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1094</v>
+        <v>0.1362</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0413</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1428</v>
+        <v>-0.924</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1594</v>
+        <v>0.605</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.3022</v>
+        <v>-1.529</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9287</v>
+        <v>-4.4343</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2985</v>
+        <v>-2.3449</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2272</v>
+        <v>-2.0894</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9695</v>
+        <v>-0.2886</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3083</v>
+        <v>-1.3022</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6613</v>
+        <v>1.0136</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.8982</v>
+        <v>-4.1457</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0097</v>
+        <v>-1.0427</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.8885</v>
+        <v>-3.103</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3907</v>
+        <v>2.5395</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.3907</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3907</v>
+        <v>2.9301</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2817</v>
+        <v>-0.7352</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1899</v>
+        <v>-0.4889</v>
       </c>
       <c r="U7" t="n">
-        <v>0.09180000000000001</v>
+        <v>-0.2464</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.8865</v>
+        <v>1.7061</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.7731</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8865</v>
+        <v>-0.067</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1869</v>
+        <v>-1.3271</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1826</v>
+        <v>0.2759</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0044</v>
+        <v>-1.603</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.0766</v>
+        <v>-1.1792</v>
       </c>
       <c r="H8" t="n">
-        <v>0.23</v>
+        <v>-0.8416</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.3065</v>
+        <v>-0.3375</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3801</v>
+        <v>1.6222</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7188</v>
+        <v>0.88</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6613</v>
+        <v>0.7422</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.4567</v>
+        <v>-2.8014</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4889</v>
+        <v>-1.7217</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.9678</v>
+        <v>-1.0797</v>
       </c>
       <c r="P8" t="n">
-        <v>0.586</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9534</v>
+        <v>-3.3208</v>
       </c>
       <c r="R8" t="n">
         <v>2.5395</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6829</v>
+        <v>-0.4079</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.773</v>
+        <v>-0.4628</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0902</v>
+        <v>0.0549</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9865</v>
+        <v>1.0413</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1638</v>
+        <v>2.4373</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1773</v>
+        <v>-1.3959</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9496</v>
+        <v>-1.549</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2844</v>
+        <v>0.9166</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6652</v>
+        <v>-2.4656</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.4343</v>
+        <v>-0.9287</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.3449</v>
+        <v>0.2985</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0894</v>
+        <v>-1.2272</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2886</v>
+        <v>0.9695</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.3022</v>
+        <v>0.3083</v>
       </c>
       <c r="L9" t="n">
-        <v>1.0136</v>
+        <v>0.6613</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.1457</v>
+        <v>-1.8982</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0427</v>
+        <v>-0.0097</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.103</v>
+        <v>-1.8885</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5395</v>
+        <v>0.3907</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.9301</v>
+        <v>0.3907</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.7608</v>
+        <v>-0.1245</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.3782</v>
+        <v>-0.0529</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3825</v>
+        <v>-0.0716</v>
       </c>
       <c r="V9" t="n">
-        <v>1.7061</v>
+        <v>-0.8865</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7731</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.067</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.114</v>
+        <v>-1.8979</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4263</v>
+        <v>-0.2646</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6877</v>
+        <v>-1.6332</v>
       </c>
       <c r="G10" t="n">
         <v>-1.9282</v>
@@ -1234,13 +1234,13 @@
         <v>2.1488</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0914</v>
+        <v>0.3075</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0689</v>
+        <v>0.2305</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0225</v>
+        <v>0.077</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2772</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2158</v>
+        <v>-3.7152</v>
       </c>
       <c r="E11" t="n">
-        <v>0.041</v>
+        <v>0.3237</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.2568</v>
+        <v>-4.0389</v>
       </c>
       <c r="G11" t="n">
         <v>1.2332</v>
@@ -1312,13 +1312,13 @@
         <v>1.5627</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5991</v>
+        <v>-1.0985</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.6252</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6912</v>
+        <v>-0.4733</v>
       </c>
       <c r="V11" t="n">
         <v>-3.0685</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.5457</v>
+        <v>-7.5114</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2307</v>
+        <v>-2.0603</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.315</v>
+        <v>-5.4512</v>
       </c>
       <c r="G12" t="n">
         <v>-4.787</v>
@@ -1390,13 +1390,13 @@
         <v>2.3441</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4293</v>
+        <v>-0.5365</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5698</v>
+        <v>-0.2598</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1405</v>
+        <v>-0.2766</v>
       </c>
       <c r="V12" t="n">
         <v>-3.5554</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-18.4835</v>
+        <v>-17.2728</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.0865</v>
+        <v>0.1240999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-17.3969</v>
+        <v>-17.3968</v>
       </c>
       <c r="G13" t="n">
         <v>-12.8119</v>
@@ -1468,10 +1468,10 @@
         <v>19.5343</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.746</v>
+        <v>-3.5354</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.3828</v>
+        <v>-2.1726</v>
       </c>
       <c r="U13" t="n">
         <v>-1.3627</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.5066</v>
+        <v>5.2105</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1063</v>
+        <v>2.4499</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4003</v>
+        <v>2.7606</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1439</v>
+        <v>0.6748</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.8238</v>
+        <v>-0.1481</v>
       </c>
       <c r="I14" t="n">
-        <v>2.9676</v>
+        <v>0.8229</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1862</v>
+        <v>1.5839</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.591</v>
+        <v>0.0857</v>
       </c>
       <c r="L14" t="n">
-        <v>3.7771</v>
+        <v>1.4982</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.0423</v>
+        <v>-0.9091</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2328</v>
+        <v>-0.2338</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8095</v>
+        <v>-0.6753</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9534</v>
+        <v>-1.1721</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5627</v>
+        <v>2.7348</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9292</v>
+        <v>1.0901</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0456</v>
+        <v>0.2649</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8836000000000001</v>
+        <v>0.8252</v>
       </c>
       <c r="V14" t="n">
-        <v>2.8242</v>
+        <v>1.8828</v>
       </c>
       <c r="W14" t="n">
-        <v>1.8279</v>
+        <v>1.7731</v>
       </c>
       <c r="X14" t="n">
-        <v>0.9962</v>
+        <v>0.1097</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.9902</v>
+        <v>4.8842</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1465</v>
+        <v>3.7018</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8437</v>
+        <v>1.1824</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6748</v>
+        <v>1.1439</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1481</v>
+        <v>-1.8238</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8229</v>
+        <v>2.9676</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5839</v>
+        <v>3.1862</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0857</v>
+        <v>-0.591</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4982</v>
+        <v>3.7771</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9091</v>
+        <v>-2.0423</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2338</v>
+        <v>-1.2328</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6753</v>
+        <v>-0.8095</v>
       </c>
       <c r="P15" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.5627</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-1.1721</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.7348</v>
-      </c>
       <c r="S15" t="n">
-        <v>0.8699</v>
+        <v>1.3069</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0384</v>
+        <v>0.6411</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9083</v>
+        <v>0.6657</v>
       </c>
       <c r="V15" t="n">
-        <v>1.8828</v>
+        <v>2.8242</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7731</v>
+        <v>1.8279</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1097</v>
+        <v>0.9962</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.0962</v>
+        <v>4.0441</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2036</v>
+        <v>1.5069</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8927</v>
+        <v>2.5372</v>
       </c>
       <c r="G16" t="n">
         <v>3.5394</v>
@@ -1702,13 +1702,13 @@
         <v>2.5395</v>
       </c>
       <c r="S16" t="n">
-        <v>1.233</v>
+        <v>1.1809</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2337</v>
+        <v>0.0696</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4667</v>
+        <v>1.1113</v>
       </c>
       <c r="V16" t="n">
         <v>0.8865</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.1517</v>
+        <v>3.8701</v>
       </c>
       <c r="E17" t="n">
-        <v>2.438</v>
+        <v>2.6403</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7137</v>
+        <v>1.2298</v>
       </c>
       <c r="G17" t="n">
         <v>5.4837</v>
@@ -1780,13 +1780,13 @@
         <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0121</v>
+        <v>0.7304</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0522</v>
+        <v>0.1501</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0643</v>
+        <v>0.5804</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.5321</v>
+        <v>3.3437</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0845</v>
+        <v>3.4889</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5524</v>
+        <v>-0.1452</v>
       </c>
       <c r="G18" t="n">
         <v>3.2995</v>
@@ -1858,13 +1858,13 @@
         <v>1.3674</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5255</v>
+        <v>0.2861</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5915</v>
+        <v>-0.187</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0659</v>
+        <v>0.4731</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2186</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.3075</v>
+        <v>2.1598</v>
       </c>
       <c r="E19" t="n">
-        <v>2.6761</v>
+        <v>2.4739</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3686</v>
+        <v>-0.3141</v>
       </c>
       <c r="G19" t="n">
         <v>0.4994</v>
@@ -1936,13 +1936,13 @@
         <v>2.3441</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4175</v>
+        <v>1.2697</v>
       </c>
       <c r="T19" t="n">
-        <v>0.864</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5535</v>
+        <v>0.6079</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5242</v>
+        <v>0.773</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8071</v>
+        <v>1.1104</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2829</v>
+        <v>-0.3374</v>
       </c>
       <c r="G20" t="n">
         <v>1.0644</v>
@@ -2014,13 +2014,13 @@
         <v>2.1488</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5756</v>
+        <v>-0.3267</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5309</v>
+        <v>-0.2276</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0447</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9414</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.2494</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1413</v>
+        <v>0.2425</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0475</v>
+        <v>0.007</v>
       </c>
       <c r="G21" t="n">
         <v>-0.454</v>
@@ -2092,13 +2092,13 @@
         <v>0.3907</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0847</v>
+        <v>0.0709</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.121</v>
+        <v>-0.0199</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>1.2186</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.448</v>
+        <v>-0.6697</v>
       </c>
       <c r="E22" t="n">
-        <v>3.4746</v>
+        <v>3.1713</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.9227</v>
+        <v>-3.841</v>
       </c>
       <c r="G22" t="n">
         <v>0.8562</v>
@@ -2170,13 +2170,13 @@
         <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3517</v>
+        <v>0.13</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5063</v>
+        <v>0.203</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1546</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4373</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6049</v>
+        <v>-0.8537</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0911</v>
+        <v>-0.3945</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5137</v>
+        <v>-0.4593</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7798</v>
@@ -2248,13 +2248,13 @@
         <v>0.9767</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2922</v>
+        <v>0.0433</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2642</v>
+        <v>-0.0391</v>
       </c>
       <c r="U23" t="n">
-        <v>0.028</v>
+        <v>0.0824</v>
       </c>
       <c r="V23" t="n">
         <v>1.2735</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.6662</v>
+        <v>-3.8541</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3128</v>
+        <v>-2.7173</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3533</v>
+        <v>-1.1368</v>
       </c>
       <c r="G24" t="n">
         <v>-1.5156</v>
@@ -2326,13 +2326,13 @@
         <v>0.7814</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1738</v>
+        <v>-0.3618</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2504</v>
+        <v>-0.154</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4243</v>
+        <v>-0.2078</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6093</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>18.4832</v>
+        <v>19.1573</v>
       </c>
       <c r="E25" t="n">
         <v>17.6741</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8092999999999995</v>
+        <v>1.4832</v>
       </c>
       <c r="G25" t="n">
         <v>12.8119</v>
@@ -2404,13 +2404,13 @@
         <v>17.5809</v>
       </c>
       <c r="S25" t="n">
-        <v>4.746</v>
+        <v>5.419800000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>1.3628</v>
+        <v>1.3629</v>
       </c>
       <c r="U25" t="n">
-        <v>3.383</v>
+        <v>4.057</v>
       </c>
       <c r="V25" t="n">
         <v>2.879</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484301_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484301_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,83 +549,93 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4292</v>
+        <v>1.521</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4343</v>
+        <v>1.521</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8635</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8105</v>
+        <v>1.521</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0276</v>
+        <v>0.307</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7829</v>
+        <v>1.214</v>
       </c>
       <c r="J2" t="n">
-        <v>1.7139</v>
+        <v>1.521</v>
       </c>
       <c r="K2" t="n">
-        <v>1.0655</v>
+        <v>0.307</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6484</v>
+        <v>1.214</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9034</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0379</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1344</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.3208</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1488</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1287</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.046</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.08260000000000001</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9195</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2992</v>
+        <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484301_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -636,230 +646,245 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2943</v>
+        <v>1.221</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2133</v>
+        <v>1.221</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.919</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4517</v>
+        <v>1.221</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6907</v>
+        <v>0.614</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.239</v>
+        <v>0.607</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1088</v>
+        <v>1.221</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7286</v>
+        <v>0.614</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6198</v>
+        <v>0.607</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.6571</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0379</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.6192</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5395</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8034</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3012</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5022</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2553</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2992</v>
+        <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484301_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. POCULL DURAN</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1028</v>
+        <v>0.4292</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0609</v>
+        <v>-0.4343</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0419</v>
+        <v>0.8635</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.07870000000000001</v>
+        <v>0.8105</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.254</v>
+        <v>0.0276</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1753</v>
+        <v>0.7829</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0609</v>
+        <v>1.7139</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0205</v>
+        <v>1.0655</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0405</v>
+        <v>0.6484</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1397</v>
+        <v>-0.9034</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2745</v>
+        <v>-1.0379</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1348</v>
+        <v>0.1344</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.3208</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1953</v>
+        <v>2.1488</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0138</v>
+        <v>-0.1287</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-0.046</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0138</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.9195</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2992</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484301_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>L. POCULL DURAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5742</v>
+        <v>0.1028</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4847</v>
+        <v>0.0609</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0588</v>
+        <v>0.0419</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.0766</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.23</v>
+        <v>-0.254</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.3065</v>
+        <v>0.1753</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3801</v>
+        <v>0.0609</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7188</v>
+        <v>0.0205</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6613</v>
+        <v>0.0405</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.4567</v>
+        <v>-0.1397</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4889</v>
+        <v>-0.2745</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.9678</v>
+        <v>0.1348</v>
       </c>
       <c r="P5" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5395</v>
+        <v>0.1953</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0701</v>
+        <v>-0.0138</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1058</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0357</v>
+        <v>-0.0138</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9865</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1638</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1773</v>
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484301_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -870,7 +895,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -938,6 +963,11 @@
       </c>
       <c r="X6" t="n">
         <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484301_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -948,7 +978,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1016,636 +1046,677 @@
       </c>
       <c r="X7" t="n">
         <v>-0.067</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484301_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>A. ABELLO GIRVES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3271</v>
+        <v>-0.9267</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2759</v>
+        <v>-0.0077</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.603</v>
+        <v>-0.919</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1792</v>
+        <v>-0.7693</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8416</v>
+        <v>2.0767</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3375</v>
+        <v>-2.846</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6222</v>
+        <v>1.8878</v>
       </c>
       <c r="K8" t="n">
-        <v>0.88</v>
+        <v>3.1146</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7422</v>
+        <v>-1.2268</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.8014</v>
+        <v>-2.6571</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.7217</v>
+        <v>-1.0379</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0797</v>
+        <v>-1.6192</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.3208</v>
+        <v>-2.1488</v>
       </c>
       <c r="R8" t="n">
         <v>2.5395</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4079</v>
+        <v>-0.8034</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4628</v>
+        <v>-0.3012</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0549</v>
+        <v>-0.5022</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0413</v>
+        <v>0.2553</v>
       </c>
       <c r="W8" t="n">
-        <v>2.4373</v>
+        <v>0.5545</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.3959</v>
+        <v>-0.2992</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484301_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.549</v>
+        <v>-1.3271</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9166</v>
+        <v>0.2759</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.4656</v>
+        <v>-1.603</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9287</v>
+        <v>-1.1792</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2985</v>
+        <v>-0.8416</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2272</v>
+        <v>-0.3375</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9695</v>
+        <v>1.6222</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3083</v>
+        <v>0.88</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6613</v>
+        <v>0.7422</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8982</v>
+        <v>-2.8014</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0097</v>
+        <v>-1.7217</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.8885</v>
+        <v>-1.0797</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3907</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.3208</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3907</v>
+        <v>2.5395</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1245</v>
+        <v>-0.4079</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0529</v>
+        <v>-0.4628</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0716</v>
+        <v>0.0549</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.8865</v>
+        <v>1.0413</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8865</v>
+        <v>-1.3959</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484301_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8979</v>
+        <v>-1.549</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2646</v>
+        <v>0.9166</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6332</v>
+        <v>-2.4656</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9282</v>
+        <v>-0.9287</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2955</v>
+        <v>0.2985</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.2236</v>
+        <v>-1.2272</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6536</v>
+        <v>0.9695</v>
       </c>
       <c r="K10" t="n">
-        <v>1.6398</v>
+        <v>0.3083</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0138</v>
+        <v>0.6613</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.5818</v>
+        <v>-1.8982</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3443</v>
+        <v>-0.0097</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.2375</v>
+        <v>-1.8885</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.3907</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1488</v>
+        <v>0.3907</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3075</v>
+        <v>-0.1245</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2305</v>
+        <v>-0.0529</v>
       </c>
       <c r="U10" t="n">
-        <v>0.077</v>
+        <v>-0.0716</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2772</v>
+        <v>-0.8865</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2772</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484301_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. GALVE NAVARRO</t>
+          <t>F. VILAR FERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7152</v>
+        <v>-1.8979</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3237</v>
+        <v>-0.2646</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.0389</v>
+        <v>-1.6332</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2332</v>
+        <v>-1.9282</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4528</v>
+        <v>1.2955</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6859</v>
+        <v>-3.2236</v>
       </c>
       <c r="J11" t="n">
-        <v>2.4064</v>
+        <v>1.6536</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4502</v>
+        <v>1.6398</v>
       </c>
       <c r="L11" t="n">
-        <v>1.9562</v>
+        <v>0.0138</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1733</v>
+        <v>-3.5818</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.903</v>
+        <v>-0.3443</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2702</v>
+        <v>-3.2375</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3441</v>
+        <v>-2.1488</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5627</v>
+        <v>2.1488</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0985</v>
+        <v>0.3075</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6252</v>
+        <v>0.2305</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4733</v>
+        <v>0.077</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.0685</v>
+        <v>-0.2772</v>
       </c>
       <c r="W11" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.9551</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484301_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. HERETER MARCHANTE</t>
+          <t>P. CARRION SORIANO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.5114</v>
+        <v>-2.0952</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0603</v>
+        <v>-1.0363</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.4512</v>
+        <v>-1.0588</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.787</v>
+        <v>-3.5975</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.9274</v>
+        <v>-0.077</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.8596</v>
+        <v>-3.5205</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.6554</v>
+        <v>-0.1408</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.2241</v>
+        <v>0.4119</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4313</v>
+        <v>-0.5527</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.1316</v>
+        <v>-3.4567</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7032</v>
+        <v>-0.4889</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.4283</v>
+        <v>-2.9678</v>
       </c>
       <c r="P12" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3441</v>
+        <v>2.5395</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5365</v>
+        <v>-0.0701</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2598</v>
+        <v>-0.1058</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2766</v>
+        <v>0.0357</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.5554</v>
+        <v>0.9865</v>
       </c>
       <c r="W12" t="n">
-        <v>0.8317</v>
+        <v>1.1638</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.3871</v>
+        <v>-0.1773</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484301_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. GALVE NAVARRO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-17.2728</v>
+        <v>-3.7152</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1240999999999999</v>
+        <v>0.3237</v>
       </c>
       <c r="F13" t="n">
-        <v>-17.3968</v>
+        <v>-4.0389</v>
       </c>
       <c r="G13" t="n">
-        <v>-12.8119</v>
+        <v>1.2332</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.348199999999999</v>
+        <v>-0.4528</v>
       </c>
       <c r="I13" t="n">
-        <v>-11.4634</v>
+        <v>1.6859</v>
       </c>
       <c r="J13" t="n">
-        <v>11.0119</v>
+        <v>2.4064</v>
       </c>
       <c r="K13" t="n">
-        <v>6.2854</v>
+        <v>0.4502</v>
       </c>
       <c r="L13" t="n">
-        <v>4.726699999999999</v>
+        <v>1.9562</v>
       </c>
       <c r="M13" t="n">
-        <v>-23.8239</v>
+        <v>-1.1733</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.633599999999999</v>
+        <v>-0.903</v>
       </c>
       <c r="O13" t="n">
-        <v>-16.1902</v>
+        <v>-0.2702</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9533</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q13" t="n">
-        <v>-17.5808</v>
+        <v>-2.3441</v>
       </c>
       <c r="R13" t="n">
-        <v>19.5343</v>
+        <v>1.5627</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.5354</v>
+        <v>-1.0985</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.1726</v>
+        <v>-0.6252</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.3627</v>
+        <v>-0.4733</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.8789</v>
+        <v>-3.0685</v>
       </c>
       <c r="W13" t="n">
-        <v>8.865499999999999</v>
+        <v>0.8865</v>
       </c>
       <c r="X13" t="n">
-        <v>-11.7445</v>
+        <v>-3.9551</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484301_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>G. HERETER MARCHANTE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TQ-CB PRAT</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.2105</v>
+        <v>-7.5114</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4499</v>
+        <v>-2.0603</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7606</v>
+        <v>-5.4512</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6748</v>
+        <v>-4.787</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1481</v>
+        <v>-1.9274</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8229</v>
+        <v>-2.8596</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5839</v>
+        <v>-1.6554</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0857</v>
+        <v>-1.2241</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4982</v>
+        <v>-0.4313</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9091</v>
+        <v>-3.1316</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2338</v>
+        <v>-0.7032</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6753</v>
+        <v>-2.4283</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5627</v>
+        <v>1.3674</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7348</v>
+        <v>2.3441</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0901</v>
+        <v>-0.5365</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2649</v>
+        <v>-0.2598</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8252</v>
+        <v>-0.2766</v>
       </c>
       <c r="V14" t="n">
-        <v>1.8828</v>
+        <v>-3.5554</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7731</v>
+        <v>0.8317</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1097</v>
+        <v>-4.3871</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484301_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TQ-CB PRAT</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.8842</v>
+        <v>-17.2728</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7018</v>
+        <v>0.1240999999999994</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1824</v>
+        <v>-17.3968</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1439</v>
+        <v>-12.8118</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.8238</v>
+        <v>-1.348199999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>2.9676</v>
+        <v>-11.4634</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1862</v>
+        <v>11.012</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.591</v>
+        <v>6.285499999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>3.7771</v>
+        <v>4.7267</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0423</v>
+        <v>-23.8239</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2328</v>
+        <v>-7.633599999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8095</v>
+        <v>-16.1902</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.3907</v>
+        <v>1.9533</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>-17.5808</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5627</v>
+        <v>19.5343</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3069</v>
+        <v>-3.5354</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6411</v>
+        <v>-2.1726</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6657</v>
+        <v>-1.3627</v>
       </c>
       <c r="V15" t="n">
-        <v>2.8242</v>
+        <v>-2.8789</v>
       </c>
       <c r="W15" t="n">
-        <v>1.8279</v>
+        <v>8.865499999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>0.9962</v>
-      </c>
+        <v>-11.7445</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. NOGUES JARNE</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.0441</v>
+        <v>5.2105</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5069</v>
+        <v>2.4499</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5372</v>
+        <v>2.7606</v>
       </c>
       <c r="G16" t="n">
-        <v>3.5394</v>
+        <v>0.6748</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6219</v>
+        <v>-0.1481</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9175</v>
+        <v>0.8229</v>
       </c>
       <c r="J16" t="n">
-        <v>4.6529</v>
+        <v>1.5839</v>
       </c>
       <c r="K16" t="n">
-        <v>3.1952</v>
+        <v>0.0857</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4578</v>
+        <v>1.4982</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1135</v>
+        <v>-0.9091</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5733</v>
+        <v>-0.2338</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5403</v>
+        <v>-0.6753</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5627</v>
+        <v>1.5627</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.1022</v>
+        <v>-1.1721</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5395</v>
+        <v>2.7348</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1809</v>
+        <v>1.0901</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0696</v>
+        <v>0.2649</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1113</v>
+        <v>0.8252</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8865</v>
+        <v>1.8828</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8865</v>
+        <v>1.7731</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.1097</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484301_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.8701</v>
+        <v>4.8842</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6403</v>
+        <v>3.7018</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2298</v>
+        <v>1.1824</v>
       </c>
       <c r="G17" t="n">
-        <v>5.4837</v>
+        <v>1.1439</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8283</v>
+        <v>-1.8238</v>
       </c>
       <c r="I17" t="n">
-        <v>6.3121</v>
+        <v>2.9676</v>
       </c>
       <c r="J17" t="n">
-        <v>6.5924</v>
+        <v>3.1862</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5296</v>
+        <v>-0.591</v>
       </c>
       <c r="L17" t="n">
-        <v>7.122</v>
+        <v>3.7771</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1087</v>
+        <v>-2.0423</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2988</v>
+        <v>-1.2328</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8099</v>
+        <v>-0.8095</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.3441</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.1022</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7304</v>
+        <v>1.3069</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1501</v>
+        <v>0.6411</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5804</v>
+        <v>0.6657</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2.8242</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.9962</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484301_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>J. NOGUES JARNE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.3437</v>
+        <v>4.0441</v>
       </c>
       <c r="E18" t="n">
-        <v>3.4889</v>
+        <v>1.5069</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1452</v>
+        <v>2.5372</v>
       </c>
       <c r="G18" t="n">
-        <v>3.2995</v>
+        <v>3.5394</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6969</v>
+        <v>2.6219</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6026</v>
+        <v>0.9175</v>
       </c>
       <c r="J18" t="n">
-        <v>3.7894</v>
+        <v>4.6529</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5116000000000001</v>
+        <v>3.1952</v>
       </c>
       <c r="L18" t="n">
-        <v>3.2777</v>
+        <v>1.4578</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4898</v>
+        <v>-1.1135</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1852</v>
+        <v>-0.5733</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6751</v>
+        <v>-0.5403</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9767</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.3907</v>
+        <v>-4.1022</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3674</v>
+        <v>2.5395</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2861</v>
+        <v>1.1809</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.187</v>
+        <v>0.0696</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4731</v>
+        <v>1.1113</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2186</v>
+        <v>0.8865</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>0.8865</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484301_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.1598</v>
+        <v>3.3437</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4739</v>
+        <v>3.4889</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3141</v>
+        <v>-0.1452</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4994</v>
+        <v>3.2995</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2167</v>
+        <v>0.6969</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2827</v>
+        <v>2.6026</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3283</v>
+        <v>3.7894</v>
       </c>
       <c r="K19" t="n">
-        <v>1.045</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2833</v>
+        <v>3.2777</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8289</v>
+        <v>-0.4898</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8283</v>
+        <v>0.1852</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.6751</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>-0.3907</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3441</v>
+        <v>1.3674</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2697</v>
+        <v>0.2861</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6618000000000001</v>
+        <v>-0.187</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6079</v>
+        <v>0.4731</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W19" t="n">
-        <v>2.4373</v>
+        <v>0.2772</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.4373</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484301_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.773</v>
+        <v>3.0419</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1104</v>
+        <v>3.0419</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3374</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.0644</v>
+        <v>3.0419</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7549</v>
+        <v>0.614</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3095</v>
+        <v>2.4279</v>
       </c>
       <c r="J20" t="n">
-        <v>2.2328</v>
+        <v>3.0419</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1924</v>
+        <v>0.614</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0405</v>
+        <v>2.4279</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1684</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4375</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.269</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1488</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3267</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2276</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.09909999999999999</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484301_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. MACÍAS MERINO</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2494</v>
+        <v>2.1598</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2425</v>
+        <v>2.4739</v>
       </c>
       <c r="F21" t="n">
-        <v>0.007</v>
+        <v>-0.3141</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.454</v>
+        <v>0.4994</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0494</v>
+        <v>0.2167</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4047</v>
+        <v>0.2827</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0205</v>
+        <v>1.3283</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0205</v>
+        <v>1.045</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.2833</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4745</v>
+        <v>-0.8289</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0698</v>
+        <v>-0.8283</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4047</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3907</v>
+        <v>2.3441</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0709</v>
+        <v>1.2697</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0199</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.6079</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2186</v>
+        <v>2.4373</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484301_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6697</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>3.1713</v>
+        <v>-0.4017</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.841</v>
+        <v>1.2298</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8562</v>
+        <v>2.4418</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2208</v>
+        <v>-1.4423</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3646</v>
+        <v>3.8841</v>
       </c>
       <c r="J22" t="n">
-        <v>1.945</v>
+        <v>3.5505</v>
       </c>
       <c r="K22" t="n">
-        <v>1.9046</v>
+        <v>-1.1435</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0405</v>
+        <v>4.694</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0889</v>
+        <v>-1.1087</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6838</v>
+        <v>-0.2988</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4051</v>
+        <v>-0.8099</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7814</v>
+        <v>-2.3441</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.1953</v>
+        <v>-4.1022</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="S22" t="n">
-        <v>0.13</v>
+        <v>0.7304</v>
       </c>
       <c r="T22" t="n">
-        <v>0.203</v>
+        <v>0.1501</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.07290000000000001</v>
+        <v>0.5804</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.6559</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484301_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. SMALLWOOD</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8537</v>
+        <v>0.773</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3945</v>
+        <v>1.1104</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4593</v>
+        <v>-0.3374</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.7798</v>
+        <v>1.0644</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6332</v>
+        <v>0.7549</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.1467</v>
+        <v>0.3095</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8159</v>
+        <v>2.2328</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3441</v>
+        <v>2.1924</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.4718</v>
+        <v>0.0405</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9639</v>
+        <v>-1.1684</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2891</v>
+        <v>-1.4375</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6749000000000001</v>
+        <v>0.269</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.3674</v>
+        <v>-1.1721</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9767</v>
+        <v>2.1488</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0433</v>
+        <v>-0.3267</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0391</v>
+        <v>-0.2276</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0824</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2735</v>
+        <v>-0.9414</v>
       </c>
       <c r="W23" t="n">
-        <v>1.8279</v>
+        <v>0.2772</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5545</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484301_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>I. MACIAS MERINO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.8541</v>
+        <v>0.2494</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7173</v>
+        <v>0.2425</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1368</v>
+        <v>0.007</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.5156</v>
+        <v>-0.454</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6802</v>
+        <v>-0.0494</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8354</v>
+        <v>-0.4047</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6917</v>
+        <v>0.0205</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1433</v>
+        <v>0.0205</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.835</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.8239</v>
+        <v>-0.4745</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8235</v>
+        <v>-0.0698</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0004</v>
+        <v>-0.4047</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.3674</v>
+        <v>-0.586</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.1488</v>
+        <v>-0.9767</v>
       </c>
       <c r="R24" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3618</v>
+        <v>0.0709</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.154</v>
+        <v>-0.0199</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2078</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6093</v>
+        <v>1.2186</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484301_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,318 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>19.1573</v>
+        <v>-0.6697</v>
       </c>
       <c r="E25" t="n">
-        <v>17.6741</v>
+        <v>3.1713</v>
       </c>
       <c r="F25" t="n">
-        <v>1.4832</v>
+        <v>-3.841</v>
       </c>
       <c r="G25" t="n">
+        <v>0.8562</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.2208</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.3646</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.945</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.9046</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1.0889</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.6838</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.4051</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.07290000000000001</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-3.6559</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484301_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>T. SMALLWOOD</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TQ-CB PRAT</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.8537</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.3945</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.4593</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-1.7798</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.6332</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1.1467</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.8159</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.3441</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-0.4718</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.9639</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.2891</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.6749000000000001</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-1.3674</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.0391</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.0824</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.2735</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.8279</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-0.5545</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484301_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>J. SOLE MORGADO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TQ-CB PRAT</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-3.8541</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-2.7173</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-1.1368</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-1.5156</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.6802</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.8354</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-0.6917</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.1433</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.835</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.8239</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.8235</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-1.3674</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.3618</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.154</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.2078</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-0.8865</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484301_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TQ-CB PRAT</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>19.15720000000001</v>
+      </c>
+      <c r="E28" t="n">
+        <v>17.674</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.483199999999999</v>
+      </c>
+      <c r="G28" t="n">
         <v>12.8119</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H28" t="n">
         <v>1.3482</v>
       </c>
-      <c r="I25" t="n">
-        <v>11.4635</v>
-      </c>
-      <c r="J25" t="n">
+      <c r="I28" t="n">
+        <v>11.4634</v>
+      </c>
+      <c r="J28" t="n">
         <v>23.8238</v>
       </c>
-      <c r="K25" t="n">
-        <v>7.6336</v>
-      </c>
-      <c r="L25" t="n">
-        <v>16.1903</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="K28" t="n">
+        <v>7.6337</v>
+      </c>
+      <c r="L28" t="n">
+        <v>16.1902</v>
+      </c>
+      <c r="M28" t="n">
         <v>-11.0119</v>
       </c>
-      <c r="N25" t="n">
-        <v>-6.285500000000001</v>
-      </c>
-      <c r="O25" t="n">
+      <c r="N28" t="n">
+        <v>-6.2855</v>
+      </c>
+      <c r="O28" t="n">
         <v>-4.7268</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P28" t="n">
         <v>-1.9534</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q28" t="n">
         <v>-19.5343</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R28" t="n">
         <v>17.5809</v>
       </c>
-      <c r="S25" t="n">
-        <v>5.419800000000001</v>
-      </c>
-      <c r="T25" t="n">
+      <c r="S28" t="n">
+        <v>5.4198</v>
+      </c>
+      <c r="T28" t="n">
         <v>1.3629</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U28" t="n">
         <v>4.057</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V28" t="n">
         <v>2.879</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W28" t="n">
         <v>12.0215</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X28" t="n">
         <v>-9.142799999999999</v>
       </c>
+      <c r="Y28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
